--- a/src/test/resources/testdata/DataCMS.xlsx
+++ b/src/test/resources/testdata/DataCMS.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\ProjectAutomation\Anhtester_CMS_AutomationTestingSeleniumJavaProject\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{108F51E2-00CA-431B-8A9D-49F0F9F0C794}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{217345EB-4BE1-4D6B-A598-43F9BA3F84E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
+    <sheet name="NewProduct" sheetId="2" r:id="rId2"/>
+    <sheet name="ProductInfo" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="24">
   <si>
     <t>Email</t>
   </si>
@@ -42,9 +44,6 @@
     <t>custome@example.com</t>
   </si>
   <si>
-    <t>admin@example.com</t>
-  </si>
-  <si>
     <t>Login failed with wrong password</t>
   </si>
   <si>
@@ -60,15 +59,9 @@
     <t>user</t>
   </si>
   <si>
-    <t>admin</t>
-  </si>
-  <si>
     <t>12345</t>
   </si>
   <si>
-    <t>123456</t>
-  </si>
-  <si>
     <t>Password</t>
   </si>
   <si>
@@ -79,12 +72,43 @@
   </si>
   <si>
     <t>ExpectedResult</t>
+  </si>
+  <si>
+    <t>ProductName</t>
+  </si>
+  <si>
+    <t>SellerName</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>Inhouse product</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Kiểm tra thông tin sản phẩm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+$100,000,000.00</t>
+  </si>
+  <si>
+    <t>dell g15</t>
+  </si>
+  <si>
+    <t>Dell</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
+  </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -142,7 +166,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -165,18 +189,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -458,7 +501,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.140625" style="2" customWidth="1"/>
@@ -474,7 +517,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -483,7 +526,7 @@
         <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -494,13 +537,13 @@
         <v>123456</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -508,76 +551,282 @@
         <v>4</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5">
+        <v>123456</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="5" t="s">
+      <c r="E4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="5" t="s">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5" t="s">
         <v>9</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5">
-        <v>123456</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>10</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>7</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C8" s="3"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C7" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{0D7AD376-F56E-44A6-B957-CF8A45282C12}"/>
     <hyperlink ref="A3" r:id="rId2" xr:uid="{4CD5156C-B8D5-4AFF-AC47-0E355154544E}"/>
-    <hyperlink ref="A4" r:id="rId3" xr:uid="{03E10A00-1BDB-4E20-9ACE-CE2823B91613}"/>
-    <hyperlink ref="A6" r:id="rId4" xr:uid="{4EC13BFD-BA03-409D-A748-32390627D96A}"/>
+    <hyperlink ref="A5" r:id="rId3" xr:uid="{4EC13BFD-BA03-409D-A748-32390627D96A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId5"/>
+  <pageSetup orientation="portrait" r:id="rId4"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35773BB2-78C5-472F-920D-64B227F15414}">
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.7109375" style="6" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="6" customWidth="1"/>
+    <col min="4" max="4" width="31.42578125" style="6" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="7"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A93D7BE-6500-439C-926E-62B42E63D252}">
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="21" style="6" customWidth="1"/>
+    <col min="2" max="2" width="25.5703125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="26" style="6" customWidth="1"/>
+    <col min="4" max="4" width="17.7109375" style="6" customWidth="1"/>
+    <col min="5" max="5" width="28.85546875" style="6" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/src/test/resources/testdata/DataCMS.xlsx
+++ b/src/test/resources/testdata/DataCMS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\ProjectAutomation\Anhtester_CMS_AutomationTestingSeleniumJavaProject\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{217345EB-4BE1-4D6B-A598-43F9BA3F84E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A383B902-EBC2-4AF6-8789-B6BC4E635BFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="31">
   <si>
     <t>Email</t>
   </si>
@@ -100,6 +100,27 @@
   </si>
   <si>
     <t>Dell</t>
+  </si>
+  <si>
+    <t>Screnario</t>
+  </si>
+  <si>
+    <t>Coca cola</t>
+  </si>
+  <si>
+    <t>nước giải khác</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>E2E Checkout</t>
+  </si>
+  <si>
+    <t>AddressIndex</t>
+  </si>
+  <si>
+    <t>OrderNote</t>
   </si>
 </sst>
 </file>
@@ -109,7 +130,7 @@
   <numFmts count="1">
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -142,6 +163,11 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -207,7 +233,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -218,6 +244,18 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="8" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -609,107 +647,72 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35773BB2-78C5-472F-920D-64B227F15414}">
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.7109375" style="6" customWidth="1"/>
-    <col min="2" max="2" width="17.5703125" style="6" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" style="6" customWidth="1"/>
-    <col min="4" max="4" width="31.42578125" style="6" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="6"/>
+    <col min="1" max="1" width="16.7109375" style="13" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" style="13" customWidth="1"/>
+    <col min="3" max="4" width="23.5703125" style="13" customWidth="1"/>
+    <col min="5" max="8" width="31.42578125" style="13" customWidth="1"/>
+    <col min="9" max="9" width="26.42578125" style="13" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="10" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="7"/>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
+      <c r="F1" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="11">
+        <v>99999999999</v>
+      </c>
+      <c r="D2" s="12">
+        <v>2</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="10">
+        <v>1</v>
+      </c>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>28</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/test/resources/testdata/DataCMS.xlsx
+++ b/src/test/resources/testdata/DataCMS.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\ProjectAutomation\Anhtester_CMS_AutomationTestingSeleniumJavaProject\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A383B902-EBC2-4AF6-8789-B6BC4E635BFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD3FA9BD-BF7B-4305-A998-FC4DD317A5C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
     <sheet name="NewProduct" sheetId="2" r:id="rId2"/>
     <sheet name="ProductInfo" sheetId="3" r:id="rId3"/>
+    <sheet name="Profile" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="50">
   <si>
     <t>Email</t>
   </si>
@@ -121,6 +122,63 @@
   </si>
   <si>
     <t>OrderNote</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name </t>
+  </si>
+  <si>
+    <t>YourPhone</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> NewPassword</t>
+  </si>
+  <si>
+    <t>ConfirmPassword</t>
+  </si>
+  <si>
+    <t>ImageName</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>Country</t>
+  </si>
+  <si>
+    <t>State</t>
+  </si>
+  <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>PostalCode</t>
+  </si>
+  <si>
+    <t>Phone</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn A</t>
+  </si>
+  <si>
+    <t>UpdateBasicInfo</t>
+  </si>
+  <si>
+    <t>UpdateAddress</t>
+  </si>
+  <si>
+    <t>UpdateInfo</t>
+  </si>
+  <si>
+    <t>Action</t>
+  </si>
+  <si>
+    <t>Run</t>
+  </si>
+  <si>
+    <t>Break</t>
+  </si>
+  <si>
+    <t>UpdateEamail</t>
   </si>
 </sst>
 </file>
@@ -130,7 +188,7 @@
   <numFmts count="1">
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -171,6 +229,13 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -192,7 +257,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -228,12 +293,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -257,6 +333,16 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -540,17 +626,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26.140625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="26.109375" style="2" customWidth="1"/>
     <col min="2" max="2" width="13" style="2" customWidth="1"/>
     <col min="3" max="3" width="18" style="2" customWidth="1"/>
-    <col min="4" max="4" width="36.85546875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="16.42578125" style="2" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="2"/>
+    <col min="4" max="4" width="36.88671875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="16.44140625" style="2" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -567,7 +653,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
@@ -584,7 +670,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
@@ -601,7 +687,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="5"/>
       <c r="B4" s="5">
         <v>123456</v>
@@ -616,7 +702,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
@@ -631,7 +717,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C7" s="3"/>
     </row>
   </sheetData>
@@ -648,17 +734,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35773BB2-78C5-472F-920D-64B227F15414}">
   <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.7109375" style="13" customWidth="1"/>
-    <col min="2" max="2" width="17.5703125" style="13" customWidth="1"/>
-    <col min="3" max="4" width="23.5703125" style="13" customWidth="1"/>
-    <col min="5" max="8" width="31.42578125" style="13" customWidth="1"/>
-    <col min="9" max="9" width="26.42578125" style="13" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="13"/>
+    <col min="1" max="1" width="16.6640625" style="13" customWidth="1"/>
+    <col min="2" max="2" width="17.5546875" style="13" customWidth="1"/>
+    <col min="3" max="4" width="23.5546875" style="13" customWidth="1"/>
+    <col min="5" max="8" width="31.44140625" style="13" customWidth="1"/>
+    <col min="9" max="9" width="26.44140625" style="13" customWidth="1"/>
+    <col min="10" max="16384" width="9.109375" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
         <v>15</v>
       </c>
@@ -687,7 +773,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
         <v>25</v>
       </c>
@@ -722,14 +808,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A93D7BE-6500-439C-926E-62B42E63D252}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" style="6" customWidth="1"/>
-    <col min="2" max="2" width="25.5703125" style="6" customWidth="1"/>
+    <col min="2" max="2" width="25.5546875" style="6" customWidth="1"/>
     <col min="3" max="3" width="26" style="6" customWidth="1"/>
-    <col min="4" max="4" width="17.7109375" style="6" customWidth="1"/>
-    <col min="5" max="5" width="28.85546875" style="6" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="6"/>
+    <col min="4" max="4" width="17.6640625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="28.88671875" style="6" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -832,4 +918,151 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F0F799A-650E-4596-A2DE-CD31EBC4C274}">
+  <dimension ref="A1:M5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="17.33203125" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" customWidth="1"/>
+    <col min="3" max="3" width="16.21875" customWidth="1"/>
+    <col min="4" max="4" width="19.21875" customWidth="1"/>
+    <col min="5" max="5" width="20.109375" customWidth="1"/>
+    <col min="6" max="6" width="15.33203125" customWidth="1"/>
+    <col min="7" max="7" width="11.77734375" customWidth="1"/>
+    <col min="8" max="8" width="10.21875" customWidth="1"/>
+    <col min="9" max="9" width="11.44140625" customWidth="1"/>
+    <col min="10" max="10" width="16.5546875" customWidth="1"/>
+    <col min="11" max="11" width="15.44140625" customWidth="1"/>
+    <col min="12" max="12" width="18.88671875" customWidth="1"/>
+    <col min="13" max="13" width="17.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="H1" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="I1" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="J1" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="K1" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="L1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="14">
+        <v>123456789</v>
+      </c>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="M2" s="14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" s="14"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="M3" s="14" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="M4" s="14" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5" s="14"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="14"/>
+      <c r="L5" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="M5" s="14" t="s">
+        <v>48</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>